--- a/archive/legacy_assets/predicted_SI.xlsx
+++ b/archive/legacy_assets/predicted_SI.xlsx
@@ -1,13 +1,13 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J120"/>
+  <dimension ref="A1:J84"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -711,12 +711,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Enterococcus faecium</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Glycopeptides</t>
+          <t>Trimethoprim-derivatives</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -726,16 +726,16 @@
         <v>2029</v>
       </c>
       <c r="E8" t="n">
-        <v>153</v>
+        <v>140</v>
       </c>
       <c r="F8" t="n">
-        <v>168</v>
+        <v>159</v>
       </c>
       <c r="G8" t="n">
-        <v>1.218917721974236</v>
+        <v>1.015445288708241</v>
       </c>
       <c r="H8" t="n">
-        <v>1.259682515515928</v>
+        <v>1.072414562207262</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -743,18 +743,18 @@
         </is>
       </c>
       <c r="J8" t="n">
-        <v>26.57064748149987</v>
+        <v>20.50807269882524</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>Trimethoprim-derivatives</t>
+          <t>Penicillins</t>
         </is>
       </c>
       <c r="C9" t="n">
@@ -764,16 +764,16 @@
         <v>2029</v>
       </c>
       <c r="E9" t="n">
-        <v>140</v>
+        <v>134</v>
       </c>
       <c r="F9" t="n">
-        <v>159</v>
+        <v>131</v>
       </c>
       <c r="G9" t="n">
-        <v>1.015445288708241</v>
+        <v>0.8501514024731784</v>
       </c>
       <c r="H9" t="n">
-        <v>1.072414562207262</v>
+        <v>0.840836920978844</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -781,18 +781,18 @@
         </is>
       </c>
       <c r="J9" t="n">
-        <v>20.50807269882524</v>
+        <v>24.7307781676182</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>Penicillins</t>
+          <t>Aminoglycosides</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -802,16 +802,16 @@
         <v>2029</v>
       </c>
       <c r="E10" t="n">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="F10" t="n">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G10" t="n">
-        <v>0.8501514024731784</v>
+        <v>0.8221773415787759</v>
       </c>
       <c r="H10" t="n">
-        <v>0.840836920978844</v>
+        <v>0.8313655914345222</v>
       </c>
       <c r="I10" t="inlineStr">
         <is>
@@ -819,18 +819,18 @@
         </is>
       </c>
       <c r="J10" t="n">
-        <v>24.7307781676182</v>
+        <v>15.07591724190151</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>Aminoglycosides</t>
+          <t>Carbapenems</t>
         </is>
       </c>
       <c r="C11" t="n">
@@ -840,35 +840,35 @@
         <v>2029</v>
       </c>
       <c r="E11" t="n">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="F11" t="n">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="G11" t="n">
-        <v>0.8221773415787759</v>
+        <v>0.9790011013360709</v>
       </c>
       <c r="H11" t="n">
-        <v>0.8313655914345222</v>
+        <v>1.004094691773939</v>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J11" t="n">
-        <v>15.07591724190151</v>
+        <v>10.10437676892359</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Helicobacter pylori</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Carbapenems</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C12" t="n">
@@ -878,35 +878,35 @@
         <v>2029</v>
       </c>
       <c r="E12" t="n">
-        <v>123</v>
+        <v>111</v>
       </c>
       <c r="F12" t="n">
-        <v>131</v>
+        <v>115</v>
       </c>
       <c r="G12" t="n">
-        <v>0.9790011013360709</v>
+        <v>0.9474660933815249</v>
       </c>
       <c r="H12" t="n">
-        <v>1.004094691773939</v>
+        <v>0.9607544889622261</v>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J12" t="n">
-        <v>10.10437676892359</v>
+        <v>8.091026715448415</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Helicobacter pylori</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Sulfonamide-trimethoprim-combinations</t>
         </is>
       </c>
       <c r="C13" t="n">
@@ -916,16 +916,16 @@
         <v>2029</v>
       </c>
       <c r="E13" t="n">
-        <v>111</v>
+        <v>108</v>
       </c>
       <c r="F13" t="n">
-        <v>115</v>
+        <v>120</v>
       </c>
       <c r="G13" t="n">
-        <v>0.9474660933815249</v>
+        <v>0.895145496053968</v>
       </c>
       <c r="H13" t="n">
-        <v>0.9607544889622261</v>
+        <v>0.9385062468175405</v>
       </c>
       <c r="I13" t="inlineStr">
         <is>
@@ -933,18 +933,18 @@
         </is>
       </c>
       <c r="J13" t="n">
-        <v>8.091026715448415</v>
+        <v>10.13873349063689</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Sulfonamide-trimethoprim-combinations</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C14" t="n">
@@ -954,16 +954,16 @@
         <v>2029</v>
       </c>
       <c r="E14" t="n">
-        <v>108</v>
+        <v>99</v>
       </c>
       <c r="F14" t="n">
-        <v>120</v>
+        <v>104</v>
       </c>
       <c r="G14" t="n">
-        <v>0.895145496053968</v>
+        <v>0.7855485623166796</v>
       </c>
       <c r="H14" t="n">
-        <v>0.9385062468175405</v>
+        <v>0.8074855164848718</v>
       </c>
       <c r="I14" t="inlineStr">
         <is>
@@ -971,7 +971,7 @@
         </is>
       </c>
       <c r="J14" t="n">
-        <v>10.13873349063689</v>
+        <v>8.606093393731701</v>
       </c>
     </row>
     <row r="15">
@@ -1020,7 +1020,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Glycopeptides</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -1030,16 +1030,16 @@
         <v>2029</v>
       </c>
       <c r="E16" t="n">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="F16" t="n">
-        <v>104</v>
+        <v>87</v>
       </c>
       <c r="G16" t="n">
-        <v>0.7855485623166796</v>
+        <v>0.730352079433654</v>
       </c>
       <c r="H16" t="n">
-        <v>0.8074855164848718</v>
+        <v>0.725968350096911</v>
       </c>
       <c r="I16" t="inlineStr">
         <is>
@@ -1047,18 +1047,18 @@
         </is>
       </c>
       <c r="J16" t="n">
-        <v>8.606093393731701</v>
+        <v>8.120475123713844</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Pseudomonas aeruginosa</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Glycopeptides</t>
+          <t>Third-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -1068,16 +1068,16 @@
         <v>2029</v>
       </c>
       <c r="E17" t="n">
-        <v>88</v>
+        <v>82</v>
       </c>
       <c r="F17" t="n">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="G17" t="n">
-        <v>0.730352079433654</v>
+        <v>0.7680813910419968</v>
       </c>
       <c r="H17" t="n">
-        <v>0.725968350096911</v>
+        <v>0.8018108870017202</v>
       </c>
       <c r="I17" t="inlineStr">
         <is>
@@ -1085,18 +1085,18 @@
         </is>
       </c>
       <c r="J17" t="n">
-        <v>8.120475123713844</v>
+        <v>21.24848425624123</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>Third-generation-cephalosporins</t>
+          <t>Fluoroquinolones</t>
         </is>
       </c>
       <c r="C18" t="n">
@@ -1106,16 +1106,16 @@
         <v>2029</v>
       </c>
       <c r="E18" t="n">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="F18" t="n">
-        <v>89</v>
+        <v>80</v>
       </c>
       <c r="G18" t="n">
-        <v>0.7680813910419968</v>
+        <v>0.6367934646739999</v>
       </c>
       <c r="H18" t="n">
-        <v>0.8018108870017202</v>
+        <v>0.6496044852505278</v>
       </c>
       <c r="I18" t="inlineStr">
         <is>
@@ -1123,18 +1123,18 @@
         </is>
       </c>
       <c r="J18" t="n">
-        <v>21.24848425624123</v>
+        <v>12.74571639444505</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>Fluoroquinolones</t>
+          <t>Penicillins</t>
         </is>
       </c>
       <c r="C19" t="n">
@@ -1144,16 +1144,16 @@
         <v>2029</v>
       </c>
       <c r="E19" t="n">
-        <v>77</v>
+        <v>72</v>
       </c>
       <c r="F19" t="n">
-        <v>80</v>
+        <v>84</v>
       </c>
       <c r="G19" t="n">
-        <v>0.6367934646739999</v>
+        <v>0.617345091422993</v>
       </c>
       <c r="H19" t="n">
-        <v>0.6496044852505278</v>
+        <v>0.6798464810125182</v>
       </c>
       <c r="I19" t="inlineStr">
         <is>
@@ -1161,7 +1161,7 @@
         </is>
       </c>
       <c r="J19" t="n">
-        <v>12.74571639444505</v>
+        <v>15.73965451577697</v>
       </c>
     </row>
     <row r="20">
@@ -1205,12 +1205,12 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>Penicillins</t>
+          <t>Carbapenems</t>
         </is>
       </c>
       <c r="C21" t="n">
@@ -1220,35 +1220,35 @@
         <v>2029</v>
       </c>
       <c r="E21" t="n">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="F21" t="n">
-        <v>84</v>
+        <v>71</v>
       </c>
       <c r="G21" t="n">
-        <v>0.617345091422993</v>
+        <v>0.6518479811878173</v>
       </c>
       <c r="H21" t="n">
-        <v>0.6798464810125182</v>
+        <v>0.6670010548273044</v>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J21" t="n">
-        <v>15.73965451577697</v>
+        <v>11.91071367370867</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Helicobacter pylori</t>
+          <t>Pseudomonas aeruginosa</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>Fluoroquinolones</t>
+          <t>Carbapenems</t>
         </is>
       </c>
       <c r="C22" t="n">
@@ -1258,16 +1258,16 @@
         <v>2029</v>
       </c>
       <c r="E22" t="n">
-        <v>71</v>
+        <v>66</v>
       </c>
       <c r="F22" t="n">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="G22" t="n">
-        <v>0.708497644312712</v>
+        <v>0.7586215880144234</v>
       </c>
       <c r="H22" t="n">
-        <v>0.7394093424693933</v>
+        <v>0.7832852353037245</v>
       </c>
       <c r="I22" t="inlineStr">
         <is>
@@ -1275,18 +1275,18 @@
         </is>
       </c>
       <c r="J22" t="n">
-        <v>31.67790883014785</v>
+        <v>12.05352467092333</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Pseudomonas aeruginosa</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>Carbapenems</t>
+          <t>Fluoroquinolones</t>
         </is>
       </c>
       <c r="C23" t="n">
@@ -1296,35 +1296,35 @@
         <v>2029</v>
       </c>
       <c r="E23" t="n">
+        <v>63</v>
+      </c>
+      <c r="F23" t="n">
         <v>68</v>
       </c>
-      <c r="F23" t="n">
-        <v>71</v>
-      </c>
       <c r="G23" t="n">
-        <v>0.6518479811878173</v>
+        <v>0.6287442309984672</v>
       </c>
       <c r="H23" t="n">
-        <v>0.6670010548273044</v>
+        <v>0.6595287627412922</v>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J23" t="n">
-        <v>11.91071367370867</v>
+        <v>24.87701442286552</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa</t>
+          <t>Helicobacter pylori</t>
         </is>
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>Carbapenems</t>
+          <t>Imidazoles</t>
         </is>
       </c>
       <c r="C24" t="n">
@@ -1334,16 +1334,16 @@
         <v>2029</v>
       </c>
       <c r="E24" t="n">
-        <v>66</v>
+        <v>61</v>
       </c>
       <c r="F24" t="n">
-        <v>70</v>
+        <v>64</v>
       </c>
       <c r="G24" t="n">
-        <v>0.7586215880144234</v>
+        <v>0.7651351318284441</v>
       </c>
       <c r="H24" t="n">
-        <v>0.7832852353037245</v>
+        <v>0.7818511801661132</v>
       </c>
       <c r="I24" t="inlineStr">
         <is>
@@ -1351,18 +1351,18 @@
         </is>
       </c>
       <c r="J24" t="n">
-        <v>12.05352467092333</v>
+        <v>8.772103055789852</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>Fluoroquinolones</t>
+          <t>Beta-lactam/beta-lactamase-inhibitor</t>
         </is>
       </c>
       <c r="C25" t="n">
@@ -1372,16 +1372,16 @@
         <v>2029</v>
       </c>
       <c r="E25" t="n">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F25" t="n">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="G25" t="n">
-        <v>0.6287442309984672</v>
+        <v>0.7334354700159895</v>
       </c>
       <c r="H25" t="n">
-        <v>0.6595287627412922</v>
+        <v>0.778615562341779</v>
       </c>
       <c r="I25" t="inlineStr">
         <is>
@@ -1389,18 +1389,18 @@
         </is>
       </c>
       <c r="J25" t="n">
-        <v>24.87701442286552</v>
+        <v>7.859441451082082</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Helicobacter pylori</t>
+          <t>Salmonella enterica</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>Imidazoles</t>
+          <t>Fluoroquinolones</t>
         </is>
       </c>
       <c r="C26" t="n">
@@ -1410,35 +1410,35 @@
         <v>2029</v>
       </c>
       <c r="E26" t="n">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F26" t="n">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="G26" t="n">
-        <v>0.7651351318284441</v>
+        <v>0.7224663124240551</v>
       </c>
       <c r="H26" t="n">
-        <v>0.7818511801661132</v>
+        <v>0.7410264912224118</v>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J26" t="n">
-        <v>8.772103055789852</v>
+        <v>4.382943702710341</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Salmonella enterica</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>Fluoroquinolones</t>
+          <t>Second-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C27" t="n">
@@ -1448,35 +1448,35 @@
         <v>2029</v>
       </c>
       <c r="E27" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F27" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="G27" t="n">
-        <v>0.7224663124240551</v>
+        <v>0.7318182515786451</v>
       </c>
       <c r="H27" t="n">
-        <v>0.7410264912224118</v>
+        <v>0.7852882059575705</v>
       </c>
       <c r="I27" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J27" t="n">
-        <v>4.382943702710341</v>
+        <v>8.416919729180833</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>Beta-lactam/beta-lactamase-inhibitor</t>
+          <t>Lincosamides</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1486,16 +1486,16 @@
         <v>2029</v>
       </c>
       <c r="E28" t="n">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="F28" t="n">
-        <v>66</v>
+        <v>57</v>
       </c>
       <c r="G28" t="n">
-        <v>0.7334354700159895</v>
+        <v>0.6563092883935822</v>
       </c>
       <c r="H28" t="n">
-        <v>0.778615562341779</v>
+        <v>0.6466201601316135</v>
       </c>
       <c r="I28" t="inlineStr">
         <is>
@@ -1503,18 +1503,18 @@
         </is>
       </c>
       <c r="J28" t="n">
-        <v>7.859441451082082</v>
+        <v>14.24201271075685</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Acinetobacter baumannii</t>
         </is>
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>Lincosamides</t>
+          <t>Carbapenems</t>
         </is>
       </c>
       <c r="C29" t="n">
@@ -1524,35 +1524,35 @@
         <v>2029</v>
       </c>
       <c r="E29" t="n">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F29" t="n">
         <v>57</v>
       </c>
       <c r="G29" t="n">
-        <v>0.6563092883935822</v>
+        <v>0.7452290032911693</v>
       </c>
       <c r="H29" t="n">
-        <v>0.6466201601316135</v>
+        <v>0.7561400021450257</v>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J29" t="n">
-        <v>14.24201271075685</v>
+        <v>14.51312263708803</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>Second-generation-cephalosporins</t>
+          <t>Aminoglycosides</t>
         </is>
       </c>
       <c r="C30" t="n">
@@ -1562,16 +1562,16 @@
         <v>2029</v>
       </c>
       <c r="E30" t="n">
-        <v>58</v>
+        <v>53</v>
       </c>
       <c r="F30" t="n">
-        <v>66</v>
+        <v>59</v>
       </c>
       <c r="G30" t="n">
-        <v>0.7318182515786451</v>
+        <v>0.5259809956342809</v>
       </c>
       <c r="H30" t="n">
-        <v>0.7852882059575705</v>
+        <v>0.5657751756892995</v>
       </c>
       <c r="I30" t="inlineStr">
         <is>
@@ -1579,18 +1579,18 @@
         </is>
       </c>
       <c r="J30" t="n">
-        <v>8.416919729180833</v>
+        <v>16.28469831565101</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Acinetobacter baumannii</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>Carbapenems</t>
+          <t>Fluoroquinolones</t>
         </is>
       </c>
       <c r="C31" t="n">
@@ -1600,16 +1600,16 @@
         <v>2029</v>
       </c>
       <c r="E31" t="n">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="F31" t="n">
-        <v>57</v>
+        <v>51</v>
       </c>
       <c r="G31" t="n">
-        <v>0.7452290032911693</v>
+        <v>0.4735683607516696</v>
       </c>
       <c r="H31" t="n">
-        <v>0.7561400021450257</v>
+        <v>0.4887199442023433</v>
       </c>
       <c r="I31" t="inlineStr">
         <is>
@@ -1617,18 +1617,18 @@
         </is>
       </c>
       <c r="J31" t="n">
-        <v>14.51312263708803</v>
+        <v>23.95950368535706</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>Aminoglycosides</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C32" t="n">
@@ -1638,16 +1638,16 @@
         <v>2029</v>
       </c>
       <c r="E32" t="n">
-        <v>53</v>
+        <v>48</v>
       </c>
       <c r="F32" t="n">
-        <v>59</v>
+        <v>61</v>
       </c>
       <c r="G32" t="n">
-        <v>0.5259809956342809</v>
+        <v>0.430218869015917</v>
       </c>
       <c r="H32" t="n">
-        <v>0.5657751756892995</v>
+        <v>0.5389104496358017</v>
       </c>
       <c r="I32" t="inlineStr">
         <is>
@@ -1655,18 +1655,18 @@
         </is>
       </c>
       <c r="J32" t="n">
-        <v>16.28469831565101</v>
+        <v>16.79577108345717</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa</t>
+          <t>Enterococcus faecalis</t>
         </is>
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>Aminoglycosides</t>
+          <t>Glycopeptides</t>
         </is>
       </c>
       <c r="C33" t="n">
@@ -1676,16 +1676,16 @@
         <v>2029</v>
       </c>
       <c r="E33" t="n">
-        <v>50</v>
+        <v>46</v>
       </c>
       <c r="F33" t="n">
-        <v>51</v>
+        <v>48</v>
       </c>
       <c r="G33" t="n">
-        <v>0.5454736659139154</v>
+        <v>0.7757734188003087</v>
       </c>
       <c r="H33" t="n">
-        <v>0.5532908910841234</v>
+        <v>0.7908885539092194</v>
       </c>
       <c r="I33" t="inlineStr">
         <is>
@@ -1693,18 +1693,18 @@
         </is>
       </c>
       <c r="J33" t="n">
-        <v>30.24202836792739</v>
+        <v>5.915743582118907</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Pseudomonas aeruginosa</t>
         </is>
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>Fluoroquinolones</t>
+          <t>Penicillins</t>
         </is>
       </c>
       <c r="C34" t="n">
@@ -1714,35 +1714,35 @@
         <v>2029</v>
       </c>
       <c r="E34" t="n">
-        <v>49</v>
+        <v>46</v>
       </c>
       <c r="F34" t="n">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="G34" t="n">
-        <v>0.4735683607516696</v>
+        <v>0.4720661929099854</v>
       </c>
       <c r="H34" t="n">
-        <v>0.4887199442023433</v>
+        <v>0.5052771290170388</v>
       </c>
       <c r="I34" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J34" t="n">
-        <v>23.95950368535706</v>
+        <v>11.15986825894109</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Salmonella enterica</t>
         </is>
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Penicillins</t>
         </is>
       </c>
       <c r="C35" t="n">
@@ -1752,16 +1752,16 @@
         <v>2029</v>
       </c>
       <c r="E35" t="n">
-        <v>48</v>
+        <v>44</v>
       </c>
       <c r="F35" t="n">
-        <v>61</v>
+        <v>45</v>
       </c>
       <c r="G35" t="n">
-        <v>0.430218869015917</v>
+        <v>0.5725111428880509</v>
       </c>
       <c r="H35" t="n">
-        <v>0.5389104496358017</v>
+        <v>0.5793270114661739</v>
       </c>
       <c r="I35" t="inlineStr">
         <is>
@@ -1769,18 +1769,18 @@
         </is>
       </c>
       <c r="J35" t="n">
-        <v>16.79577108345717</v>
+        <v>23.54051838967725</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Campylobacter jejuni</t>
+          <t>Neisseria gonorrhoeae</t>
         </is>
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Third-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C36" t="n">
@@ -1790,16 +1790,16 @@
         <v>2029</v>
       </c>
       <c r="E36" t="n">
-        <v>47</v>
+        <v>43</v>
       </c>
       <c r="F36" t="n">
-        <v>56</v>
+        <v>44</v>
       </c>
       <c r="G36" t="n">
-        <v>0.9429358266813517</v>
+        <v>0.7571772587707366</v>
       </c>
       <c r="H36" t="n">
-        <v>1.015843747106388</v>
+        <v>0.7669854964569482</v>
       </c>
       <c r="I36" t="inlineStr">
         <is>
@@ -1807,18 +1807,18 @@
         </is>
       </c>
       <c r="J36" t="n">
-        <v>47.58507246072246</v>
+        <v>4.78652685640494</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa</t>
+          <t>Salmonella enterica</t>
         </is>
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>Penicillins</t>
+          <t>Third-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C37" t="n">
@@ -1828,16 +1828,16 @@
         <v>2029</v>
       </c>
       <c r="E37" t="n">
-        <v>46</v>
+        <v>42</v>
       </c>
       <c r="F37" t="n">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="G37" t="n">
-        <v>0.4720661929099854</v>
+        <v>0.5931235709905964</v>
       </c>
       <c r="H37" t="n">
-        <v>0.5052771290170388</v>
+        <v>0.6507186833693763</v>
       </c>
       <c r="I37" t="inlineStr">
         <is>
@@ -1845,18 +1845,18 @@
         </is>
       </c>
       <c r="J37" t="n">
-        <v>11.15986825894109</v>
+        <v>9.749205179203395</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Enterococcus faecalis</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>Glycopeptides</t>
+          <t>Second-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C38" t="n">
@@ -1866,16 +1866,16 @@
         <v>2029</v>
       </c>
       <c r="E38" t="n">
+        <v>41</v>
+      </c>
+      <c r="F38" t="n">
         <v>46</v>
       </c>
-      <c r="F38" t="n">
-        <v>48</v>
-      </c>
       <c r="G38" t="n">
-        <v>0.7757734188003087</v>
+        <v>0.536625264809899</v>
       </c>
       <c r="H38" t="n">
-        <v>0.7908885539092194</v>
+        <v>0.5826070689387459</v>
       </c>
       <c r="I38" t="inlineStr">
         <is>
@@ -1883,18 +1883,18 @@
         </is>
       </c>
       <c r="J38" t="n">
-        <v>5.915743582118907</v>
+        <v>13.92673290562042</v>
       </c>
     </row>
     <row r="39">
       <c r="A39" t="inlineStr">
         <is>
-          <t>Salmonella enterica</t>
+          <t>Streptococcus pneumoniae</t>
         </is>
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>Penicillins</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C39" t="n">
@@ -1904,35 +1904,35 @@
         <v>2029</v>
       </c>
       <c r="E39" t="n">
-        <v>44</v>
+        <v>40</v>
       </c>
       <c r="F39" t="n">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="G39" t="n">
-        <v>0.5725111428880509</v>
+        <v>0.612823488078855</v>
       </c>
       <c r="H39" t="n">
-        <v>0.5793270114661739</v>
+        <v>0.6142311679839063</v>
       </c>
       <c r="I39" t="inlineStr">
         <is>
-          <t>no</t>
+          <t>yes</t>
         </is>
       </c>
       <c r="J39" t="n">
-        <v>23.54051838967725</v>
+        <v>7.241672071835522</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>Neisseria gonorrhoeae</t>
+          <t>Mycobacterium tuberculosis</t>
         </is>
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>Third-generation-cephalosporins</t>
+          <t>Aminoglycosides</t>
         </is>
       </c>
       <c r="C40" t="n">
@@ -1942,16 +1942,16 @@
         <v>2029</v>
       </c>
       <c r="E40" t="n">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="F40" t="n">
-        <v>44</v>
+        <v>32</v>
       </c>
       <c r="G40" t="n">
-        <v>0.7571772587707366</v>
+        <v>0.3906903253172871</v>
       </c>
       <c r="H40" t="n">
-        <v>0.7669854964569482</v>
+        <v>0.3605213135780032</v>
       </c>
       <c r="I40" t="inlineStr">
         <is>
@@ -1959,18 +1959,18 @@
         </is>
       </c>
       <c r="J40" t="n">
-        <v>4.78652685640494</v>
+        <v>9.405743123243324</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>Salmonella enterica</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>Third-generation-cephalosporins</t>
+          <t>Sulfonamide-trimethoprim-combinations</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1980,16 +1980,16 @@
         <v>2029</v>
       </c>
       <c r="E41" t="n">
+        <v>34</v>
+      </c>
+      <c r="F41" t="n">
         <v>42</v>
       </c>
-      <c r="F41" t="n">
-        <v>48</v>
-      </c>
       <c r="G41" t="n">
-        <v>0.5931235709905964</v>
+        <v>0.4785057268188184</v>
       </c>
       <c r="H41" t="n">
-        <v>0.6507186833693763</v>
+        <v>0.5607268041238609</v>
       </c>
       <c r="I41" t="inlineStr">
         <is>
@@ -1997,7 +1997,7 @@
         </is>
       </c>
       <c r="J41" t="n">
-        <v>9.749205179203395</v>
+        <v>13.28599751130573</v>
       </c>
     </row>
     <row r="42">
@@ -2008,7 +2008,7 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>Second-generation-cephalosporins</t>
+          <t>Amphenicols</t>
         </is>
       </c>
       <c r="C42" t="n">
@@ -2018,16 +2018,16 @@
         <v>2029</v>
       </c>
       <c r="E42" t="n">
-        <v>41</v>
+        <v>33</v>
       </c>
       <c r="F42" t="n">
-        <v>46</v>
+        <v>35</v>
       </c>
       <c r="G42" t="n">
-        <v>0.536625264809899</v>
+        <v>0.4759463249038216</v>
       </c>
       <c r="H42" t="n">
-        <v>0.5826070689387459</v>
+        <v>0.5060540892806709</v>
       </c>
       <c r="I42" t="inlineStr">
         <is>
@@ -2035,18 +2035,18 @@
         </is>
       </c>
       <c r="J42" t="n">
-        <v>13.92673290562042</v>
+        <v>20.88899679499637</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Streptococcus pneumoniae</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Third-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C43" t="n">
@@ -2056,30 +2056,30 @@
         <v>2029</v>
       </c>
       <c r="E43" t="n">
-        <v>40</v>
+        <v>32</v>
       </c>
       <c r="F43" t="n">
-        <v>40</v>
+        <v>37</v>
       </c>
       <c r="G43" t="n">
-        <v>0.612823488078855</v>
+        <v>0.2827044426443561</v>
       </c>
       <c r="H43" t="n">
-        <v>0.6142311679839063</v>
+        <v>0.3447164054891756</v>
       </c>
       <c r="I43" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="J43" t="n">
-        <v>7.241672071835522</v>
+        <v>19.30524576171661</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>Campylobacter jejuni</t>
+          <t>Neisseria gonorrhoeae</t>
         </is>
       </c>
       <c r="B44" t="inlineStr">
@@ -2094,16 +2094,16 @@
         <v>2029</v>
       </c>
       <c r="E44" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F44" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G44" t="n">
-        <v>0.8218091730903827</v>
+        <v>0.5819793787479808</v>
       </c>
       <c r="H44" t="n">
-        <v>0.8619152093508491</v>
+        <v>0.5974218378028937</v>
       </c>
       <c r="I44" t="inlineStr">
         <is>
@@ -2111,18 +2111,18 @@
         </is>
       </c>
       <c r="J44" t="n">
-        <v>39.94037572348499</v>
+        <v>12.69273315868253</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Salmonella enterica</t>
         </is>
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>Phosphonics</t>
+          <t>Aminoglycosides</t>
         </is>
       </c>
       <c r="C45" t="n">
@@ -2132,16 +2132,16 @@
         <v>2029</v>
       </c>
       <c r="E45" t="n">
-        <v>38</v>
+        <v>30</v>
       </c>
       <c r="F45" t="n">
-        <v>49</v>
+        <v>29</v>
       </c>
       <c r="G45" t="n">
-        <v>0.6187951500221109</v>
+        <v>0.44289132646422</v>
       </c>
       <c r="H45" t="n">
-        <v>0.7298084334524773</v>
+        <v>0.427074393790505</v>
       </c>
       <c r="I45" t="inlineStr">
         <is>
@@ -2149,18 +2149,18 @@
         </is>
       </c>
       <c r="J45" t="n">
-        <v>44.81296851381001</v>
+        <v>13.19879367792396</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>Mycobacterium tuberculosis</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>Aminoglycosides</t>
+          <t>Trimethoprim-derivatives</t>
         </is>
       </c>
       <c r="C46" t="n">
@@ -2170,16 +2170,16 @@
         <v>2029</v>
       </c>
       <c r="E46" t="n">
-        <v>34</v>
+        <v>30</v>
       </c>
       <c r="F46" t="n">
-        <v>32</v>
+        <v>37</v>
       </c>
       <c r="G46" t="n">
-        <v>0.3906903253172871</v>
+        <v>0.4325128553661326</v>
       </c>
       <c r="H46" t="n">
-        <v>0.3605213135780032</v>
+        <v>0.5214379594993712</v>
       </c>
       <c r="I46" t="inlineStr">
         <is>
@@ -2187,18 +2187,18 @@
         </is>
       </c>
       <c r="J46" t="n">
-        <v>9.405743123243324</v>
+        <v>24.13876221942635</v>
       </c>
     </row>
     <row r="47">
       <c r="A47" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>Sulfonamide-trimethoprim-combinations</t>
+          <t>Glycylcyclines</t>
         </is>
       </c>
       <c r="C47" t="n">
@@ -2208,16 +2208,16 @@
         <v>2029</v>
       </c>
       <c r="E47" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F47" t="n">
-        <v>42</v>
+        <v>31</v>
       </c>
       <c r="G47" t="n">
-        <v>0.4785057268188184</v>
+        <v>0.4642005867770418</v>
       </c>
       <c r="H47" t="n">
-        <v>0.5607268041238609</v>
+        <v>0.5086773189739302</v>
       </c>
       <c r="I47" t="inlineStr">
         <is>
@@ -2225,18 +2225,18 @@
         </is>
       </c>
       <c r="J47" t="n">
-        <v>13.28599751130573</v>
+        <v>16.93110445587214</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>First-generation-cephalosporins</t>
+          <t>Beta-lactam/beta-lactamase-inhibitor_anti-pseudomonal</t>
         </is>
       </c>
       <c r="C48" t="n">
@@ -2246,16 +2246,16 @@
         <v>2029</v>
       </c>
       <c r="E48" t="n">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="F48" t="n">
-        <v>41</v>
+        <v>31</v>
       </c>
       <c r="G48" t="n">
-        <v>0.5752980898077353</v>
+        <v>0.4668028274720366</v>
       </c>
       <c r="H48" t="n">
-        <v>0.6501295291793934</v>
+        <v>0.5134911045201391</v>
       </c>
       <c r="I48" t="inlineStr">
         <is>
@@ -2263,18 +2263,18 @@
         </is>
       </c>
       <c r="J48" t="n">
-        <v>41.17937602457466</v>
+        <v>15.07270921511292</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>Amphenicols</t>
+          <t>Tetracyclines</t>
         </is>
       </c>
       <c r="C49" t="n">
@@ -2284,16 +2284,16 @@
         <v>2029</v>
       </c>
       <c r="E49" t="n">
-        <v>33</v>
+        <v>26</v>
       </c>
       <c r="F49" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G49" t="n">
-        <v>0.4759463249038216</v>
+        <v>0.2403283220096983</v>
       </c>
       <c r="H49" t="n">
-        <v>0.5060540892806709</v>
+        <v>0.341329375622631</v>
       </c>
       <c r="I49" t="inlineStr">
         <is>
@@ -2301,18 +2301,18 @@
         </is>
       </c>
       <c r="J49" t="n">
-        <v>20.88899679499637</v>
+        <v>17.3435312125895</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Salmonella enterica</t>
+          <t>Helicobacter pylori</t>
         </is>
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Penicillins</t>
         </is>
       </c>
       <c r="C50" t="n">
@@ -2322,16 +2322,16 @@
         <v>2029</v>
       </c>
       <c r="E50" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F50" t="n">
-        <v>32</v>
+        <v>28</v>
       </c>
       <c r="G50" t="n">
-        <v>0.49066401414062</v>
+        <v>0.2690529291889561</v>
       </c>
       <c r="H50" t="n">
-        <v>0.4878194751530305</v>
+        <v>0.292009319904533</v>
       </c>
       <c r="I50" t="inlineStr">
         <is>
@@ -2339,18 +2339,18 @@
         </is>
       </c>
       <c r="J50" t="n">
-        <v>25.40122252001398</v>
+        <v>13.53437292203027</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Pseudomonas aeruginosa</t>
         </is>
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>Third-generation-cephalosporins</t>
+          <t>Beta-lactam/beta-lactamase-inhibitor_anti-pseudomonal</t>
         </is>
       </c>
       <c r="C51" t="n">
@@ -2360,16 +2360,16 @@
         <v>2029</v>
       </c>
       <c r="E51" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="F51" t="n">
-        <v>37</v>
+        <v>27</v>
       </c>
       <c r="G51" t="n">
-        <v>0.2827044426443561</v>
+        <v>0.4796060272701255</v>
       </c>
       <c r="H51" t="n">
-        <v>0.3447164054891756</v>
+        <v>0.5024784069492061</v>
       </c>
       <c r="I51" t="inlineStr">
         <is>
@@ -2377,18 +2377,18 @@
         </is>
       </c>
       <c r="J51" t="n">
-        <v>19.30524576171661</v>
+        <v>10.23516770451769</v>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>Salmonella enterica</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>Aminoglycosides</t>
+          <t>Sulfonamide-trimethoprim-combinations</t>
         </is>
       </c>
       <c r="C52" t="n">
@@ -2398,16 +2398,16 @@
         <v>2029</v>
       </c>
       <c r="E52" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F52" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="G52" t="n">
-        <v>0.44289132646422</v>
+        <v>0.309352801889605</v>
       </c>
       <c r="H52" t="n">
-        <v>0.427074393790505</v>
+        <v>0.3263571077129876</v>
       </c>
       <c r="I52" t="inlineStr">
         <is>
@@ -2415,18 +2415,18 @@
         </is>
       </c>
       <c r="J52" t="n">
-        <v>13.19879367792396</v>
+        <v>9.43145036694629</v>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>Trimethoprim-derivatives</t>
+          <t>Beta-lactam/beta-lactamase-inhibitor_anti-pseudomonal</t>
         </is>
       </c>
       <c r="C53" t="n">
@@ -2436,16 +2436,16 @@
         <v>2029</v>
       </c>
       <c r="E53" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F53" t="n">
-        <v>37</v>
+        <v>28</v>
       </c>
       <c r="G53" t="n">
-        <v>0.4325128553661326</v>
+        <v>0.3453512763469384</v>
       </c>
       <c r="H53" t="n">
-        <v>0.5214379594993712</v>
+        <v>0.3897098508267349</v>
       </c>
       <c r="I53" t="inlineStr">
         <is>
@@ -2453,18 +2453,18 @@
         </is>
       </c>
       <c r="J53" t="n">
-        <v>24.13876221942635</v>
+        <v>12.41451650350251</v>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>Streptococcus agalactiae</t>
+          <t>Enterococcus faecalis</t>
         </is>
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>Lincosamides</t>
+          <t>Tetracyclines</t>
         </is>
       </c>
       <c r="C54" t="n">
@@ -2474,16 +2474,16 @@
         <v>2029</v>
       </c>
       <c r="E54" t="n">
-        <v>30</v>
+        <v>25</v>
       </c>
       <c r="F54" t="n">
-        <v>33</v>
+        <v>27</v>
       </c>
       <c r="G54" t="n">
-        <v>0.8010328457048652</v>
+        <v>0.5029209196264155</v>
       </c>
       <c r="H54" t="n">
-        <v>0.8366951688224469</v>
+        <v>0.5331781523858607</v>
       </c>
       <c r="I54" t="inlineStr">
         <is>
@@ -2491,18 +2491,18 @@
         </is>
       </c>
       <c r="J54" t="n">
-        <v>47.81509890784222</v>
+        <v>15.90327209494377</v>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>Neisseria gonorrhoeae</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>Fluoroquinolones</t>
+          <t>Beta-lactam/beta-lactamase-inhibitor</t>
         </is>
       </c>
       <c r="C55" t="n">
@@ -2512,16 +2512,16 @@
         <v>2029</v>
       </c>
       <c r="E55" t="n">
+        <v>24</v>
+      </c>
+      <c r="F55" t="n">
         <v>30</v>
       </c>
-      <c r="F55" t="n">
-        <v>31</v>
-      </c>
       <c r="G55" t="n">
-        <v>0.5819793787479808</v>
+        <v>0.4300956031611285</v>
       </c>
       <c r="H55" t="n">
-        <v>0.5974218378028937</v>
+        <v>0.5088089694801923</v>
       </c>
       <c r="I55" t="inlineStr">
         <is>
@@ -2529,18 +2529,18 @@
         </is>
       </c>
       <c r="J55" t="n">
-        <v>12.69273315868253</v>
+        <v>18.32872261437137</v>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>Salmonella enterica</t>
+          <t>Pseudomonas aeruginosa</t>
         </is>
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Fourth-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C56" t="n">
@@ -2550,16 +2550,16 @@
         <v>2029</v>
       </c>
       <c r="E56" t="n">
-        <v>29</v>
+        <v>23</v>
       </c>
       <c r="F56" t="n">
-        <v>39</v>
+        <v>25</v>
       </c>
       <c r="G56" t="n">
-        <v>0.4563946402120875</v>
+        <v>0.47832696948371</v>
       </c>
       <c r="H56" t="n">
-        <v>0.5792760089410725</v>
+        <v>0.5134988472317312</v>
       </c>
       <c r="I56" t="inlineStr">
         <is>
@@ -2567,18 +2567,18 @@
         </is>
       </c>
       <c r="J56" t="n">
-        <v>46.12365319836528</v>
+        <v>11.83015226299159</v>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>Beta-lactam/beta-lactamase-inhibitor_anti-pseudomonal</t>
+          <t>Trimethoprim-derivatives</t>
         </is>
       </c>
       <c r="C57" t="n">
@@ -2588,16 +2588,16 @@
         <v>2029</v>
       </c>
       <c r="E57" t="n">
-        <v>28</v>
+        <v>22</v>
       </c>
       <c r="F57" t="n">
-        <v>31</v>
+        <v>22</v>
       </c>
       <c r="G57" t="n">
-        <v>0.4668028274720366</v>
+        <v>0.2771116644963463</v>
       </c>
       <c r="H57" t="n">
-        <v>0.5134911045201391</v>
+        <v>0.2727968421847911</v>
       </c>
       <c r="I57" t="inlineStr">
         <is>
@@ -2605,7 +2605,7 @@
         </is>
       </c>
       <c r="J57" t="n">
-        <v>15.07270921511292</v>
+        <v>18.46621535578246</v>
       </c>
     </row>
     <row r="58">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>Glycylcyclines</t>
+          <t>Nitrofuran-derivatives</t>
         </is>
       </c>
       <c r="C58" t="n">
@@ -2626,16 +2626,16 @@
         <v>2029</v>
       </c>
       <c r="E58" t="n">
-        <v>28</v>
+        <v>21</v>
       </c>
       <c r="F58" t="n">
-        <v>31</v>
+        <v>24</v>
       </c>
       <c r="G58" t="n">
-        <v>0.4642005867770418</v>
+        <v>0.4109141344808032</v>
       </c>
       <c r="H58" t="n">
-        <v>0.5086773189739302</v>
+        <v>0.4755900471262964</v>
       </c>
       <c r="I58" t="inlineStr">
         <is>
@@ -2643,18 +2643,18 @@
         </is>
       </c>
       <c r="J58" t="n">
-        <v>16.93110445587214</v>
+        <v>14.85528798103131</v>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa</t>
+          <t>Enterococcus faecium</t>
         </is>
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>Beta-lactam/beta-lactamase-inhibitor_anti-pseudomonal</t>
+          <t>Oxazolidinones</t>
         </is>
       </c>
       <c r="C59" t="n">
@@ -2664,16 +2664,16 @@
         <v>2029</v>
       </c>
       <c r="E59" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F59" t="n">
-        <v>27</v>
+        <v>20</v>
       </c>
       <c r="G59" t="n">
-        <v>0.4796060272701255</v>
+        <v>0.4870918228072811</v>
       </c>
       <c r="H59" t="n">
-        <v>0.5024784069492061</v>
+        <v>0.5024493695731933</v>
       </c>
       <c r="I59" t="inlineStr">
         <is>
@@ -2681,18 +2681,18 @@
         </is>
       </c>
       <c r="J59" t="n">
-        <v>10.23516770451769</v>
+        <v>14.10027015415705</v>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Acinetobacter baumannii</t>
         </is>
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>Beta-lactamase-inhibitors</t>
+          <t>Fluoroquinolones</t>
         </is>
       </c>
       <c r="C60" t="n">
@@ -2702,16 +2702,16 @@
         <v>2029</v>
       </c>
       <c r="E60" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F60" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G60" t="n">
-        <v>0.3519790308227537</v>
+        <v>0.2132296907587805</v>
       </c>
       <c r="H60" t="n">
-        <v>0.3923405601764827</v>
+        <v>0.2032192238970947</v>
       </c>
       <c r="I60" t="inlineStr">
         <is>
@@ -2719,13 +2719,13 @@
         </is>
       </c>
       <c r="J60" t="n">
-        <v>25.07700564679193</v>
+        <v>21.48445873543648</v>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Neisseria gonorrhoeae</t>
         </is>
       </c>
       <c r="B61" t="inlineStr">
@@ -2740,16 +2740,16 @@
         <v>2029</v>
       </c>
       <c r="E61" t="n">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="F61" t="n">
-        <v>34</v>
+        <v>22</v>
       </c>
       <c r="G61" t="n">
-        <v>0.2403283220096983</v>
+        <v>0.4412122031785266</v>
       </c>
       <c r="H61" t="n">
-        <v>0.341329375622631</v>
+        <v>0.4806698547503252</v>
       </c>
       <c r="I61" t="inlineStr">
         <is>
@@ -2757,18 +2757,18 @@
         </is>
       </c>
       <c r="J61" t="n">
-        <v>17.3435312125895</v>
+        <v>22.02672963143239</v>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>Helicobacter pylori</t>
+          <t>Streptococcus pneumoniae</t>
         </is>
       </c>
       <c r="B62" t="inlineStr">
         <is>
-          <t>Penicillins</t>
+          <t>Tetracyclines</t>
         </is>
       </c>
       <c r="C62" t="n">
@@ -2778,16 +2778,16 @@
         <v>2029</v>
       </c>
       <c r="E62" t="n">
-        <v>26</v>
+        <v>19</v>
       </c>
       <c r="F62" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G62" t="n">
-        <v>0.2690529291889561</v>
+        <v>0.278206542067942</v>
       </c>
       <c r="H62" t="n">
-        <v>0.292009319904533</v>
+        <v>0.3105255081320208</v>
       </c>
       <c r="I62" t="inlineStr">
         <is>
@@ -2795,7 +2795,7 @@
         </is>
       </c>
       <c r="J62" t="n">
-        <v>13.53437292203027</v>
+        <v>15.55108477810051</v>
       </c>
     </row>
     <row r="63">
@@ -2806,7 +2806,7 @@
       </c>
       <c r="B63" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Tetracyclines</t>
         </is>
       </c>
       <c r="C63" t="n">
@@ -2816,16 +2816,16 @@
         <v>2029</v>
       </c>
       <c r="E63" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="F63" t="n">
-        <v>28</v>
+        <v>20</v>
       </c>
       <c r="G63" t="n">
-        <v>0.64770497708316</v>
+        <v>0.4697883250047243</v>
       </c>
       <c r="H63" t="n">
-        <v>0.6749329360609568</v>
+        <v>0.5248496955731041</v>
       </c>
       <c r="I63" t="inlineStr">
         <is>
@@ -2833,18 +2833,18 @@
         </is>
       </c>
       <c r="J63" t="n">
-        <v>32.62478447866731</v>
+        <v>21.64110764285963</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Klebsiella pneumoniae</t>
         </is>
       </c>
       <c r="B64" t="inlineStr">
         <is>
-          <t>Sulfonamide-trimethoprim-combinations</t>
+          <t>Fourth-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C64" t="n">
@@ -2854,16 +2854,16 @@
         <v>2029</v>
       </c>
       <c r="E64" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F64" t="n">
-        <v>26</v>
+        <v>18</v>
       </c>
       <c r="G64" t="n">
-        <v>0.309352801889605</v>
+        <v>0.2859598692250964</v>
       </c>
       <c r="H64" t="n">
-        <v>0.3263571077129876</v>
+        <v>0.3129889934881527</v>
       </c>
       <c r="I64" t="inlineStr">
         <is>
@@ -2871,18 +2871,18 @@
         </is>
       </c>
       <c r="J64" t="n">
-        <v>9.43145036694629</v>
+        <v>19.84829035424533</v>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Enterococcus faecalis</t>
         </is>
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>Beta-lactam/beta-lactamase-inhibitor_anti-pseudomonal</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C65" t="n">
@@ -2892,16 +2892,16 @@
         <v>2029</v>
       </c>
       <c r="E65" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F65" t="n">
-        <v>28</v>
+        <v>18</v>
       </c>
       <c r="G65" t="n">
-        <v>0.3453512763469384</v>
+        <v>0.3650391200955883</v>
       </c>
       <c r="H65" t="n">
-        <v>0.3897098508267349</v>
+        <v>0.3892267651139838</v>
       </c>
       <c r="I65" t="inlineStr">
         <is>
@@ -2909,18 +2909,18 @@
         </is>
       </c>
       <c r="J65" t="n">
-        <v>12.41451650350251</v>
+        <v>13.11248207792986</v>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="inlineStr">
         <is>
-          <t>Enterococcus faecalis</t>
+          <t>Haemophilus influenzae</t>
         </is>
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Penicillins</t>
         </is>
       </c>
       <c r="C66" t="n">
@@ -2930,16 +2930,16 @@
         <v>2029</v>
       </c>
       <c r="E66" t="n">
-        <v>25</v>
+        <v>17</v>
       </c>
       <c r="F66" t="n">
-        <v>27</v>
+        <v>16</v>
       </c>
       <c r="G66" t="n">
-        <v>0.5029209196264155</v>
+        <v>0.4398095489693827</v>
       </c>
       <c r="H66" t="n">
-        <v>0.5331781523858607</v>
+        <v>0.4158569448667018</v>
       </c>
       <c r="I66" t="inlineStr">
         <is>
@@ -2947,18 +2947,18 @@
         </is>
       </c>
       <c r="J66" t="n">
-        <v>15.90327209494377</v>
+        <v>13.83322731694649</v>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Salmonella enterica</t>
         </is>
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>Monobactams</t>
+          <t>Sulfonamide-trimethoprim-combinations</t>
         </is>
       </c>
       <c r="C67" t="n">
@@ -2968,16 +2968,16 @@
         <v>2029</v>
       </c>
       <c r="E67" t="n">
-        <v>24</v>
+        <v>17</v>
       </c>
       <c r="F67" t="n">
-        <v>29</v>
+        <v>19</v>
       </c>
       <c r="G67" t="n">
-        <v>0.4385702373163647</v>
+        <v>0.3538010127865128</v>
       </c>
       <c r="H67" t="n">
-        <v>0.5125084805835309</v>
+        <v>0.3987077313180611</v>
       </c>
       <c r="I67" t="inlineStr">
         <is>
@@ -2985,18 +2985,18 @@
         </is>
       </c>
       <c r="J67" t="n">
-        <v>44.13808758487805</v>
+        <v>13.4210667458878</v>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Staphylococcus aureus</t>
         </is>
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>Beta-lactam/beta-lactamase-inhibitor</t>
+          <t>Amphenicols</t>
         </is>
       </c>
       <c r="C68" t="n">
@@ -3006,16 +3006,16 @@
         <v>2029</v>
       </c>
       <c r="E68" t="n">
-        <v>24</v>
+        <v>16</v>
       </c>
       <c r="F68" t="n">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="G68" t="n">
-        <v>0.4300956031611285</v>
+        <v>0.211425389079309</v>
       </c>
       <c r="H68" t="n">
-        <v>0.5088089694801923</v>
+        <v>0.2474241836001487</v>
       </c>
       <c r="I68" t="inlineStr">
         <is>
@@ -3023,18 +3023,18 @@
         </is>
       </c>
       <c r="J68" t="n">
-        <v>18.32872261437137</v>
+        <v>11.56036807350337</v>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="inlineStr">
         <is>
-          <t>Pseudomonas aeruginosa</t>
+          <t>Salmonella enterica</t>
         </is>
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>Fourth-generation-cephalosporins</t>
+          <t>Amphenicols</t>
         </is>
       </c>
       <c r="C69" t="n">
@@ -3044,16 +3044,16 @@
         <v>2029</v>
       </c>
       <c r="E69" t="n">
-        <v>23</v>
+        <v>15</v>
       </c>
       <c r="F69" t="n">
-        <v>25</v>
+        <v>15</v>
       </c>
       <c r="G69" t="n">
-        <v>0.47832696948371</v>
+        <v>0.399693378448551</v>
       </c>
       <c r="H69" t="n">
-        <v>0.5134988472317312</v>
+        <v>0.3901815075897279</v>
       </c>
       <c r="I69" t="inlineStr">
         <is>
@@ -3061,18 +3061,18 @@
         </is>
       </c>
       <c r="J69" t="n">
-        <v>11.83015226299159</v>
+        <v>19.54217623528691</v>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="inlineStr">
         <is>
-          <t>Mycobacterium abscessus</t>
+          <t>Campylobacter coli</t>
         </is>
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>Macrolides</t>
+          <t>Fluoroquinolones</t>
         </is>
       </c>
       <c r="C70" t="n">
@@ -3082,16 +3082,16 @@
         <v>2029</v>
       </c>
       <c r="E70" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F70" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="G70" t="n">
-        <v>0.6855471382844216</v>
+        <v>0.4273782030442672</v>
       </c>
       <c r="H70" t="n">
-        <v>0.7189248615442414</v>
+        <v>0.4332994565565464</v>
       </c>
       <c r="I70" t="inlineStr">
         <is>
@@ -3099,18 +3099,18 @@
         </is>
       </c>
       <c r="J70" t="n">
-        <v>39.88441473203451</v>
+        <v>23.78244461515768</v>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Mycoplasmoides genitalium</t>
         </is>
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>Trimethoprim-derivatives</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C71" t="n">
@@ -3120,16 +3120,16 @@
         <v>2029</v>
       </c>
       <c r="E71" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F71" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="G71" t="n">
-        <v>0.2771116644963463</v>
+        <v>0.4460001953378236</v>
       </c>
       <c r="H71" t="n">
-        <v>0.2727968421847911</v>
+        <v>0.4485706766248951</v>
       </c>
       <c r="I71" t="inlineStr">
         <is>
@@ -3137,18 +3137,18 @@
         </is>
       </c>
       <c r="J71" t="n">
-        <v>18.46621535578246</v>
+        <v>14.91991941229707</v>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="inlineStr">
         <is>
-          <t>Acinetobacter baumannii</t>
+          <t>Campylobacter jejuni</t>
         </is>
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>Aminoglycosides</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C72" t="n">
@@ -3158,16 +3158,16 @@
         <v>2029</v>
       </c>
       <c r="E72" t="n">
-        <v>22</v>
+        <v>14</v>
       </c>
       <c r="F72" t="n">
-        <v>20</v>
+        <v>15</v>
       </c>
       <c r="G72" t="n">
-        <v>0.2616743653957698</v>
+        <v>0.4554108813230935</v>
       </c>
       <c r="H72" t="n">
-        <v>0.2201634827795376</v>
+        <v>0.4771989178119607</v>
       </c>
       <c r="I72" t="inlineStr">
         <is>
@@ -3175,18 +3175,18 @@
         </is>
       </c>
       <c r="J72" t="n">
-        <v>28.3911775757574</v>
+        <v>17.36455934537124</v>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="inlineStr">
         <is>
-          <t>Staphylococcus aureus</t>
+          <t>Salmonella enterica</t>
         </is>
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>Lipopeptides</t>
+          <t>Trimethoprim-derivatives</t>
         </is>
       </c>
       <c r="C73" t="n">
@@ -3196,16 +3196,16 @@
         <v>2029</v>
       </c>
       <c r="E73" t="n">
-        <v>21</v>
+        <v>13</v>
       </c>
       <c r="F73" t="n">
-        <v>21</v>
+        <v>14</v>
       </c>
       <c r="G73" t="n">
-        <v>0.3053863241392925</v>
+        <v>0.2533799457441572</v>
       </c>
       <c r="H73" t="n">
-        <v>0.3070842144956702</v>
+        <v>0.2681090566240896</v>
       </c>
       <c r="I73" t="inlineStr">
         <is>
@@ -3213,18 +3213,18 @@
         </is>
       </c>
       <c r="J73" t="n">
-        <v>43.1052055208382</v>
+        <v>20.31634113418007</v>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Enterobacter cloacae</t>
         </is>
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>Nitrofuran-derivatives</t>
+          <t>Third-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C74" t="n">
@@ -3234,16 +3234,16 @@
         <v>2029</v>
       </c>
       <c r="E74" t="n">
-        <v>21</v>
+        <v>12</v>
       </c>
       <c r="F74" t="n">
-        <v>24</v>
+        <v>13</v>
       </c>
       <c r="G74" t="n">
-        <v>0.4109141344808032</v>
+        <v>0.3316156218122934</v>
       </c>
       <c r="H74" t="n">
-        <v>0.4755900471262964</v>
+        <v>0.352298078666452</v>
       </c>
       <c r="I74" t="inlineStr">
         <is>
@@ -3251,18 +3251,18 @@
         </is>
       </c>
       <c r="J74" t="n">
-        <v>14.85528798103131</v>
+        <v>15.93342650708624</v>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="inlineStr">
         <is>
-          <t>Acinetobacter baumannii</t>
+          <t>Streptococcus pneumoniae</t>
         </is>
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>Fluoroquinolones</t>
+          <t>Third-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C75" t="n">
@@ -3272,16 +3272,16 @@
         <v>2029</v>
       </c>
       <c r="E75" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F75" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="G75" t="n">
-        <v>0.2132296907587805</v>
+        <v>0.1095871226652274</v>
       </c>
       <c r="H75" t="n">
-        <v>0.2032192238970947</v>
+        <v>0.0881530656545324</v>
       </c>
       <c r="I75" t="inlineStr">
         <is>
@@ -3289,18 +3289,18 @@
         </is>
       </c>
       <c r="J75" t="n">
-        <v>21.48445873543648</v>
+        <v>20.35648057022654</v>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Enterococcus faecium</t>
         </is>
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>Glycylcyclines</t>
+          <t>Tetracyclines</t>
         </is>
       </c>
       <c r="C76" t="n">
@@ -3310,16 +3310,16 @@
         <v>2029</v>
       </c>
       <c r="E76" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F76" t="n">
-        <v>20</v>
+        <v>13</v>
       </c>
       <c r="G76" t="n">
-        <v>0.3976731037473142</v>
+        <v>0.1489661802620004</v>
       </c>
       <c r="H76" t="n">
-        <v>0.4053562020525827</v>
+        <v>0.1592268907630912</v>
       </c>
       <c r="I76" t="inlineStr">
         <is>
@@ -3327,18 +3327,18 @@
         </is>
       </c>
       <c r="J76" t="n">
-        <v>30.37419003652087</v>
+        <v>20.82430157481807</v>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="inlineStr">
         <is>
-          <t>Enterococcus faecium</t>
+          <t>Acinetobacter baumannii</t>
         </is>
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>Oxazolidinones</t>
+          <t>Glycylcyclines</t>
         </is>
       </c>
       <c r="C77" t="n">
@@ -3348,16 +3348,16 @@
         <v>2029</v>
       </c>
       <c r="E77" t="n">
-        <v>20</v>
+        <v>12</v>
       </c>
       <c r="F77" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G77" t="n">
-        <v>0.4870918228072811</v>
+        <v>0.2995431481844288</v>
       </c>
       <c r="H77" t="n">
-        <v>0.5024493695731933</v>
+        <v>0.287742636542726</v>
       </c>
       <c r="I77" t="inlineStr">
         <is>
@@ -3365,18 +3365,18 @@
         </is>
       </c>
       <c r="J77" t="n">
-        <v>14.10027015415705</v>
+        <v>24.87999044417614</v>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="inlineStr">
         <is>
-          <t>Neisseria gonorrhoeae</t>
+          <t>Enterococcus faecium</t>
         </is>
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C78" t="n">
@@ -3386,16 +3386,16 @@
         <v>2029</v>
       </c>
       <c r="E78" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F78" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G78" t="n">
-        <v>0.4412122031785266</v>
+        <v>0.1161440075068356</v>
       </c>
       <c r="H78" t="n">
-        <v>0.4806698547503252</v>
+        <v>0.124020270960528</v>
       </c>
       <c r="I78" t="inlineStr">
         <is>
@@ -3403,18 +3403,18 @@
         </is>
       </c>
       <c r="J78" t="n">
-        <v>22.02672963143239</v>
+        <v>20.96651980317871</v>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>Campylobacter coli</t>
+          <t>Staphylococcus epidermidis</t>
         </is>
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Penicillins</t>
         </is>
       </c>
       <c r="C79" t="n">
@@ -3424,16 +3424,16 @@
         <v>2029</v>
       </c>
       <c r="E79" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="F79" t="n">
-        <v>22</v>
+        <v>11</v>
       </c>
       <c r="G79" t="n">
-        <v>0.6017126082470992</v>
+        <v>0.2671449752641393</v>
       </c>
       <c r="H79" t="n">
-        <v>0.6464679300428977</v>
+        <v>0.2678481730624225</v>
       </c>
       <c r="I79" t="inlineStr">
         <is>
@@ -3441,18 +3441,18 @@
         </is>
       </c>
       <c r="J79" t="n">
-        <v>28.61506678168095</v>
+        <v>24.49258294760917</v>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="inlineStr">
         <is>
-          <t>Klebsiella pneumoniae</t>
+          <t>Streptococcus pyogenes</t>
         </is>
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>Second-generation-cephalosporins</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -3462,16 +3462,16 @@
         <v>2029</v>
       </c>
       <c r="E80" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="F80" t="n">
-        <v>23</v>
+        <v>10</v>
       </c>
       <c r="G80" t="n">
-        <v>0.301457893672022</v>
+        <v>0.3088272064201179</v>
       </c>
       <c r="H80" t="n">
-        <v>0.365727834041182</v>
+        <v>0.3132827272867045</v>
       </c>
       <c r="I80" t="inlineStr">
         <is>
@@ -3479,18 +3479,18 @@
         </is>
       </c>
       <c r="J80" t="n">
-        <v>27.28166388512585</v>
+        <v>17.28943877287773</v>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t>Escherichia coli</t>
+          <t>Stenotrophomonas maltophilia</t>
         </is>
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>Fourth-generation-cephalosporins</t>
+          <t>Third-generation-cephalosporins</t>
         </is>
       </c>
       <c r="C81" t="n">
@@ -3500,16 +3500,16 @@
         <v>2029</v>
       </c>
       <c r="E81" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F81" t="n">
-        <v>19</v>
+        <v>11</v>
       </c>
       <c r="G81" t="n">
-        <v>0.2602280668610339</v>
+        <v>0.3059409377286515</v>
       </c>
       <c r="H81" t="n">
-        <v>0.2705624868224068</v>
+        <v>0.3444331189228456</v>
       </c>
       <c r="I81" t="inlineStr">
         <is>
@@ -3517,18 +3517,18 @@
         </is>
       </c>
       <c r="J81" t="n">
-        <v>35.9174534311692</v>
+        <v>20.46178265347313</v>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="inlineStr">
         <is>
-          <t>Streptococcus pneumoniae</t>
+          <t>Staphylococcus epidermidis</t>
         </is>
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Macrolides</t>
         </is>
       </c>
       <c r="C82" t="n">
@@ -3538,16 +3538,16 @@
         <v>2029</v>
       </c>
       <c r="E82" t="n">
-        <v>19</v>
+        <v>10</v>
       </c>
       <c r="F82" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="G82" t="n">
-        <v>0.278206542067942</v>
+        <v>0.2859481773858492</v>
       </c>
       <c r="H82" t="n">
-        <v>0.3105255081320208</v>
+        <v>0.3071417659357354</v>
       </c>
       <c r="I82" t="inlineStr">
         <is>
@@ -3555,18 +3555,18 @@
         </is>
       </c>
       <c r="J82" t="n">
-        <v>15.55108477810051</v>
+        <v>17.91631842151344</v>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="inlineStr">
         <is>
-          <t>Streptococcus agalactiae</t>
+          <t>Escherichia coli</t>
         </is>
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>Tetracyclines</t>
+          <t>Lincosamides</t>
         </is>
       </c>
       <c r="C83" t="n">
@@ -3576,16 +3576,16 @@
         <v>2029</v>
       </c>
       <c r="E83" t="n">
-        <v>18</v>
+        <v>10</v>
       </c>
       <c r="F83" t="n">
-        <v>20</v>
+        <v>11</v>
       </c>
       <c r="G83" t="n">
-        <v>0.4697883250047243</v>
+        <v>-0.1219091711874021</v>
       </c>
       <c r="H83" t="n">
-        <v>0.5248496955731041</v>
+        <v>-0.07191773300934057</v>
       </c>
       <c r="I83" t="inlineStr">
         <is>
@@ -3593,7 +3593,7 @@
         </is>
       </c>
       <c r="J83" t="n">
-        <v>21.64110764285963</v>
+        <v>18.55981365758918</v>
       </c>
     </row>
     <row r="84">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>Aminoglycosides</t>
+          <t>Fluoroquinolones</t>
         </is>
       </c>
       <c r="C84" t="n">
@@ -3614,16 +3614,16 @@
         <v>2029</v>
       </c>
       <c r="E84" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="F84" t="n">
-        <v>18</v>
+        <v>9</v>
       </c>
       <c r="G84" t="n">
-        <v>0.2816566464074262</v>
+        <v>0.008155837171667457</v>
       </c>
       <c r="H84" t="n">
-        <v>0.2846405210396534</v>
+        <v>0.0005005074335733273</v>
       </c>
       <c r="I84" t="inlineStr">
         <is>
@@ -3631,1375 +3631,7 @@
         </is>
       </c>
       <c r="J84" t="n">
-        <v>34.60727618961498</v>
-      </c>
-    </row>
-    <row r="85">
-      <c r="A85" t="inlineStr">
-        <is>
-          <t>Staphylococcus aureus</t>
-        </is>
-      </c>
-      <c r="B85" t="inlineStr">
-        <is>
-          <t>Beta-lactam/beta-lactamase-inhibitor</t>
-        </is>
-      </c>
-      <c r="C85" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D85" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E85" t="n">
-        <v>18</v>
-      </c>
-      <c r="F85" t="n">
-        <v>22</v>
-      </c>
-      <c r="G85" t="n">
-        <v>0.2654814200762847</v>
-      </c>
-      <c r="H85" t="n">
-        <v>0.3564712233537621</v>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J85" t="n">
-        <v>28.5713546208026</v>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="inlineStr">
-        <is>
-          <t>Enterococcus faecalis</t>
-        </is>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>Fluoroquinolones</t>
-        </is>
-      </c>
-      <c r="C86" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D86" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E86" t="n">
-        <v>17</v>
-      </c>
-      <c r="F86" t="n">
-        <v>17</v>
-      </c>
-      <c r="G86" t="n">
-        <v>0.3071320989776543</v>
-      </c>
-      <c r="H86" t="n">
-        <v>0.3255301346081405</v>
-      </c>
-      <c r="I86" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J86" t="n">
-        <v>30.82733259422567</v>
-      </c>
-    </row>
-    <row r="87">
-      <c r="A87" t="inlineStr">
-        <is>
-          <t>Enterococcus faecalis</t>
-        </is>
-      </c>
-      <c r="B87" t="inlineStr">
-        <is>
-          <t>Macrolides</t>
-        </is>
-      </c>
-      <c r="C87" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D87" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E87" t="n">
-        <v>17</v>
-      </c>
-      <c r="F87" t="n">
-        <v>18</v>
-      </c>
-      <c r="G87" t="n">
-        <v>0.3650391200955883</v>
-      </c>
-      <c r="H87" t="n">
-        <v>0.3892267651139838</v>
-      </c>
-      <c r="I87" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J87" t="n">
-        <v>13.11248207792986</v>
-      </c>
-    </row>
-    <row r="88">
-      <c r="A88" t="inlineStr">
-        <is>
-          <t>Klebsiella pneumoniae</t>
-        </is>
-      </c>
-      <c r="B88" t="inlineStr">
-        <is>
-          <t>Fourth-generation-cephalosporins</t>
-        </is>
-      </c>
-      <c r="C88" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D88" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E88" t="n">
-        <v>17</v>
-      </c>
-      <c r="F88" t="n">
-        <v>18</v>
-      </c>
-      <c r="G88" t="n">
-        <v>0.2859598692250964</v>
-      </c>
-      <c r="H88" t="n">
-        <v>0.3129889934881527</v>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J88" t="n">
-        <v>19.84829035424533</v>
-      </c>
-    </row>
-    <row r="89">
-      <c r="A89" t="inlineStr">
-        <is>
-          <t>Haemophilus influenzae</t>
-        </is>
-      </c>
-      <c r="B89" t="inlineStr">
-        <is>
-          <t>Penicillins</t>
-        </is>
-      </c>
-      <c r="C89" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D89" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E89" t="n">
-        <v>17</v>
-      </c>
-      <c r="F89" t="n">
-        <v>16</v>
-      </c>
-      <c r="G89" t="n">
-        <v>0.4398095489693827</v>
-      </c>
-      <c r="H89" t="n">
-        <v>0.4158569448667018</v>
-      </c>
-      <c r="I89" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J89" t="n">
-        <v>13.83322731694649</v>
-      </c>
-    </row>
-    <row r="90">
-      <c r="A90" t="inlineStr">
-        <is>
-          <t>Salmonella enterica</t>
-        </is>
-      </c>
-      <c r="B90" t="inlineStr">
-        <is>
-          <t>Sulfonamide-trimethoprim-combinations</t>
-        </is>
-      </c>
-      <c r="C90" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D90" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E90" t="n">
-        <v>17</v>
-      </c>
-      <c r="F90" t="n">
-        <v>19</v>
-      </c>
-      <c r="G90" t="n">
-        <v>0.3538010127865128</v>
-      </c>
-      <c r="H90" t="n">
-        <v>0.3987077313180611</v>
-      </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J90" t="n">
-        <v>13.4210667458878</v>
-      </c>
-    </row>
-    <row r="91">
-      <c r="A91" t="inlineStr">
-        <is>
-          <t>Enterobacter cloacae</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>Penicillins</t>
-        </is>
-      </c>
-      <c r="C91" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D91" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E91" t="n">
-        <v>17</v>
-      </c>
-      <c r="F91" t="n">
-        <v>22</v>
-      </c>
-      <c r="G91" t="n">
-        <v>0.4358291432108572</v>
-      </c>
-      <c r="H91" t="n">
-        <v>0.5327959698712579</v>
-      </c>
-      <c r="I91" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J91" t="n">
-        <v>43.85419008526385</v>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" t="inlineStr">
-        <is>
-          <t>Staphylococcus aureus</t>
-        </is>
-      </c>
-      <c r="B92" t="inlineStr">
-        <is>
-          <t>Amphenicols</t>
-        </is>
-      </c>
-      <c r="C92" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D92" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E92" t="n">
-        <v>16</v>
-      </c>
-      <c r="F92" t="n">
-        <v>17</v>
-      </c>
-      <c r="G92" t="n">
-        <v>0.211425389079309</v>
-      </c>
-      <c r="H92" t="n">
-        <v>0.2474241836001487</v>
-      </c>
-      <c r="I92" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J92" t="n">
-        <v>11.56036807350337</v>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" t="inlineStr">
-        <is>
-          <t>Mycobacterium tuberculosis</t>
-        </is>
-      </c>
-      <c r="B93" t="inlineStr">
-        <is>
-          <t>Fluoroquinolones</t>
-        </is>
-      </c>
-      <c r="C93" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D93" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E93" t="n">
-        <v>16</v>
-      </c>
-      <c r="F93" t="n">
-        <v>15</v>
-      </c>
-      <c r="G93" t="n">
-        <v>0.07091944726820865</v>
-      </c>
-      <c r="H93" t="n">
-        <v>0.02879278341605551</v>
-      </c>
-      <c r="I93" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J93" t="n">
-        <v>32.48617073856815</v>
-      </c>
-    </row>
-    <row r="94">
-      <c r="A94" t="inlineStr">
-        <is>
-          <t>Campylobacter coli</t>
-        </is>
-      </c>
-      <c r="B94" t="inlineStr">
-        <is>
-          <t>Macrolides</t>
-        </is>
-      </c>
-      <c r="C94" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D94" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E94" t="n">
-        <v>15</v>
-      </c>
-      <c r="F94" t="n">
-        <v>16</v>
-      </c>
-      <c r="G94" t="n">
-        <v>0.5074695303712236</v>
-      </c>
-      <c r="H94" t="n">
-        <v>0.543316102385929</v>
-      </c>
-      <c r="I94" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J94" t="n">
-        <v>31.79493651805609</v>
-      </c>
-    </row>
-    <row r="95">
-      <c r="A95" t="inlineStr">
-        <is>
-          <t>Salmonella enterica</t>
-        </is>
-      </c>
-      <c r="B95" t="inlineStr">
-        <is>
-          <t>Amphenicols</t>
-        </is>
-      </c>
-      <c r="C95" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D95" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E95" t="n">
-        <v>15</v>
-      </c>
-      <c r="F95" t="n">
-        <v>15</v>
-      </c>
-      <c r="G95" t="n">
-        <v>0.399693378448551</v>
-      </c>
-      <c r="H95" t="n">
-        <v>0.3901815075897279</v>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J95" t="n">
-        <v>19.54217623528691</v>
-      </c>
-    </row>
-    <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>Campylobacter jejuni</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>Macrolides</t>
-        </is>
-      </c>
-      <c r="C96" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D96" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E96" t="n">
-        <v>14</v>
-      </c>
-      <c r="F96" t="n">
-        <v>15</v>
-      </c>
-      <c r="G96" t="n">
-        <v>0.4554108813230935</v>
-      </c>
-      <c r="H96" t="n">
-        <v>0.4771989178119607</v>
-      </c>
-      <c r="I96" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J96" t="n">
-        <v>17.36455934537124</v>
-      </c>
-    </row>
-    <row r="97">
-      <c r="A97" t="inlineStr">
-        <is>
-          <t>Campylobacter coli</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>Fluoroquinolones</t>
-        </is>
-      </c>
-      <c r="C97" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D97" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E97" t="n">
-        <v>14</v>
-      </c>
-      <c r="F97" t="n">
-        <v>14</v>
-      </c>
-      <c r="G97" t="n">
-        <v>0.4273782030442672</v>
-      </c>
-      <c r="H97" t="n">
-        <v>0.4332994565565464</v>
-      </c>
-      <c r="I97" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J97" t="n">
-        <v>23.78244461515768</v>
-      </c>
-    </row>
-    <row r="98">
-      <c r="A98" t="inlineStr">
-        <is>
-          <t>Mycoplasmoides genitalium</t>
-        </is>
-      </c>
-      <c r="B98" t="inlineStr">
-        <is>
-          <t>Macrolides</t>
-        </is>
-      </c>
-      <c r="C98" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D98" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E98" t="n">
-        <v>14</v>
-      </c>
-      <c r="F98" t="n">
-        <v>14</v>
-      </c>
-      <c r="G98" t="n">
-        <v>0.4460001953378236</v>
-      </c>
-      <c r="H98" t="n">
-        <v>0.4485706766248951</v>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J98" t="n">
-        <v>14.91991941229707</v>
-      </c>
-    </row>
-    <row r="99">
-      <c r="A99" t="inlineStr">
-        <is>
-          <t>Acinetobacter baumannii</t>
-        </is>
-      </c>
-      <c r="B99" t="inlineStr">
-        <is>
-          <t>Third-generation-cephalosporins</t>
-        </is>
-      </c>
-      <c r="C99" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D99" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E99" t="n">
-        <v>13</v>
-      </c>
-      <c r="F99" t="n">
-        <v>12</v>
-      </c>
-      <c r="G99" t="n">
-        <v>0.06189196382946172</v>
-      </c>
-      <c r="H99" t="n">
-        <v>0.01509739264710985</v>
-      </c>
-      <c r="I99" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J99" t="n">
-        <v>40.50292884306576</v>
-      </c>
-    </row>
-    <row r="100">
-      <c r="A100" t="inlineStr">
-        <is>
-          <t>Salmonella enterica</t>
-        </is>
-      </c>
-      <c r="B100" t="inlineStr">
-        <is>
-          <t>Trimethoprim-derivatives</t>
-        </is>
-      </c>
-      <c r="C100" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D100" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E100" t="n">
-        <v>13</v>
-      </c>
-      <c r="F100" t="n">
-        <v>14</v>
-      </c>
-      <c r="G100" t="n">
-        <v>0.2533799457441572</v>
-      </c>
-      <c r="H100" t="n">
-        <v>0.2681090566240896</v>
-      </c>
-      <c r="I100" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J100" t="n">
-        <v>20.31634113418007</v>
-      </c>
-    </row>
-    <row r="101">
-      <c r="A101" t="inlineStr">
-        <is>
-          <t>Acinetobacter baumannii</t>
-        </is>
-      </c>
-      <c r="B101" t="inlineStr">
-        <is>
-          <t>Glycylcyclines</t>
-        </is>
-      </c>
-      <c r="C101" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D101" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E101" t="n">
-        <v>12</v>
-      </c>
-      <c r="F101" t="n">
-        <v>11</v>
-      </c>
-      <c r="G101" t="n">
-        <v>0.2995431481844288</v>
-      </c>
-      <c r="H101" t="n">
-        <v>0.287742636542726</v>
-      </c>
-      <c r="I101" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J101" t="n">
-        <v>24.87999044417614</v>
-      </c>
-    </row>
-    <row r="102">
-      <c r="A102" t="inlineStr">
-        <is>
-          <t>Enterobacter cloacae</t>
-        </is>
-      </c>
-      <c r="B102" t="inlineStr">
-        <is>
-          <t>Third-generation-cephalosporins</t>
-        </is>
-      </c>
-      <c r="C102" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D102" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E102" t="n">
-        <v>12</v>
-      </c>
-      <c r="F102" t="n">
-        <v>13</v>
-      </c>
-      <c r="G102" t="n">
-        <v>0.3316156218122934</v>
-      </c>
-      <c r="H102" t="n">
-        <v>0.352298078666452</v>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J102" t="n">
-        <v>15.93342650708624</v>
-      </c>
-    </row>
-    <row r="103">
-      <c r="A103" t="inlineStr">
-        <is>
-          <t>Streptococcus pneumoniae</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>Third-generation-cephalosporins</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D103" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E103" t="n">
-        <v>12</v>
-      </c>
-      <c r="F103" t="n">
-        <v>12</v>
-      </c>
-      <c r="G103" t="n">
-        <v>0.1095871226652274</v>
-      </c>
-      <c r="H103" t="n">
-        <v>0.0881530656545324</v>
-      </c>
-      <c r="I103" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J103" t="n">
-        <v>20.35648057022654</v>
-      </c>
-    </row>
-    <row r="104">
-      <c r="A104" t="inlineStr">
-        <is>
-          <t>Enterococcus faecium</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>Tetracyclines</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D104" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E104" t="n">
-        <v>12</v>
-      </c>
-      <c r="F104" t="n">
-        <v>13</v>
-      </c>
-      <c r="G104" t="n">
-        <v>0.1489661802620004</v>
-      </c>
-      <c r="H104" t="n">
-        <v>0.1592268907630912</v>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J104" t="n">
-        <v>20.82430157481807</v>
-      </c>
-    </row>
-    <row r="105">
-      <c r="A105" t="inlineStr">
-        <is>
-          <t>Staphylococcus epidermidis</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>Penicillins</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D105" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E105" t="n">
-        <v>11</v>
-      </c>
-      <c r="F105" t="n">
-        <v>11</v>
-      </c>
-      <c r="G105" t="n">
-        <v>0.2671449752641393</v>
-      </c>
-      <c r="H105" t="n">
-        <v>0.2678481730624225</v>
-      </c>
-      <c r="I105" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J105" t="n">
-        <v>24.49258294760917</v>
-      </c>
-    </row>
-    <row r="106">
-      <c r="A106" t="inlineStr">
-        <is>
-          <t>Listeria monocytogenes</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>Tetracyclines</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D106" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E106" t="n">
-        <v>11</v>
-      </c>
-      <c r="F106" t="n">
-        <v>12</v>
-      </c>
-      <c r="G106" t="n">
-        <v>0.4053519158381427</v>
-      </c>
-      <c r="H106" t="n">
-        <v>0.4494809645032702</v>
-      </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J106" t="n">
-        <v>26.05103612012261</v>
-      </c>
-    </row>
-    <row r="107">
-      <c r="A107" t="inlineStr">
-        <is>
-          <t>Stenotrophomonas maltophilia</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>Fluoroquinolones</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D107" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E107" t="n">
-        <v>11</v>
-      </c>
-      <c r="F107" t="n">
-        <v>12</v>
-      </c>
-      <c r="G107" t="n">
-        <v>0.3389684831198621</v>
-      </c>
-      <c r="H107" t="n">
-        <v>0.3568498743162543</v>
-      </c>
-      <c r="I107" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J107" t="n">
-        <v>28.15254331618268</v>
-      </c>
-    </row>
-    <row r="108">
-      <c r="A108" t="inlineStr">
-        <is>
-          <t>Enterococcus faecium</t>
-        </is>
-      </c>
-      <c r="B108" t="inlineStr">
-        <is>
-          <t>Macrolides</t>
-        </is>
-      </c>
-      <c r="C108" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D108" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E108" t="n">
-        <v>11</v>
-      </c>
-      <c r="F108" t="n">
-        <v>11</v>
-      </c>
-      <c r="G108" t="n">
-        <v>0.1161440075068356</v>
-      </c>
-      <c r="H108" t="n">
-        <v>0.124020270960528</v>
-      </c>
-      <c r="I108" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J108" t="n">
-        <v>20.96651980317871</v>
-      </c>
-    </row>
-    <row r="109">
-      <c r="A109" t="inlineStr">
-        <is>
-          <t>Streptococcus pyogenes</t>
-        </is>
-      </c>
-      <c r="B109" t="inlineStr">
-        <is>
-          <t>Macrolides</t>
-        </is>
-      </c>
-      <c r="C109" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D109" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E109" t="n">
-        <v>10</v>
-      </c>
-      <c r="F109" t="n">
-        <v>10</v>
-      </c>
-      <c r="G109" t="n">
-        <v>0.3088272064201179</v>
-      </c>
-      <c r="H109" t="n">
-        <v>0.3132827272867045</v>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J109" t="n">
-        <v>17.28943877287773</v>
-      </c>
-    </row>
-    <row r="110">
-      <c r="A110" t="inlineStr">
-        <is>
-          <t>Staphylococcus aureus</t>
-        </is>
-      </c>
-      <c r="B110" t="inlineStr">
-        <is>
-          <t>Oxazolidinones</t>
-        </is>
-      </c>
-      <c r="C110" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D110" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E110" t="n">
-        <v>10</v>
-      </c>
-      <c r="F110" t="n">
-        <v>10</v>
-      </c>
-      <c r="G110" t="n">
-        <v>-0.0498199693140986</v>
-      </c>
-      <c r="H110" t="n">
-        <v>-0.05452497807295442</v>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J110" t="n">
-        <v>44.19249335333076</v>
-      </c>
-    </row>
-    <row r="111">
-      <c r="A111" t="inlineStr">
-        <is>
-          <t>Escherichia coli</t>
-        </is>
-      </c>
-      <c r="B111" t="inlineStr">
-        <is>
-          <t>Lincosamides</t>
-        </is>
-      </c>
-      <c r="C111" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D111" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E111" t="n">
-        <v>10</v>
-      </c>
-      <c r="F111" t="n">
-        <v>11</v>
-      </c>
-      <c r="G111" t="n">
-        <v>-0.1219091711874021</v>
-      </c>
-      <c r="H111" t="n">
-        <v>-0.07191773300934057</v>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J111" t="n">
-        <v>18.55981365758918</v>
-      </c>
-    </row>
-    <row r="112">
-      <c r="A112" t="inlineStr">
-        <is>
-          <t>Listeria monocytogenes</t>
-        </is>
-      </c>
-      <c r="B112" t="inlineStr">
-        <is>
-          <t>Penicillins</t>
-        </is>
-      </c>
-      <c r="C112" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D112" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E112" t="n">
-        <v>10</v>
-      </c>
-      <c r="F112" t="n">
-        <v>10</v>
-      </c>
-      <c r="G112" t="n">
-        <v>0.3206424750802956</v>
-      </c>
-      <c r="H112" t="n">
-        <v>0.3291978524174648</v>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J112" t="n">
-        <v>25.02461074680669</v>
-      </c>
-    </row>
-    <row r="113">
-      <c r="A113" t="inlineStr">
-        <is>
-          <t>Stenotrophomonas maltophilia</t>
-        </is>
-      </c>
-      <c r="B113" t="inlineStr">
-        <is>
-          <t>Third-generation-cephalosporins</t>
-        </is>
-      </c>
-      <c r="C113" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D113" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E113" t="n">
-        <v>10</v>
-      </c>
-      <c r="F113" t="n">
-        <v>11</v>
-      </c>
-      <c r="G113" t="n">
-        <v>0.3059409377286515</v>
-      </c>
-      <c r="H113" t="n">
-        <v>0.3444331189228456</v>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J113" t="n">
-        <v>20.46178265347313</v>
-      </c>
-    </row>
-    <row r="114">
-      <c r="A114" t="inlineStr">
-        <is>
-          <t>Staphylococcus epidermidis</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>Macrolides</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D114" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E114" t="n">
-        <v>10</v>
-      </c>
-      <c r="F114" t="n">
-        <v>10</v>
-      </c>
-      <c r="G114" t="n">
-        <v>0.2859481773858492</v>
-      </c>
-      <c r="H114" t="n">
-        <v>0.3071417659357354</v>
-      </c>
-      <c r="I114" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J114" t="n">
-        <v>17.91631842151344</v>
-      </c>
-    </row>
-    <row r="115">
-      <c r="A115" t="inlineStr">
-        <is>
-          <t>Enterococcus faecium</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>Fluoroquinolones</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D115" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E115" t="n">
-        <v>9</v>
-      </c>
-      <c r="F115" t="n">
-        <v>9</v>
-      </c>
-      <c r="G115" t="n">
-        <v>0.008155837171667457</v>
-      </c>
-      <c r="H115" t="n">
-        <v>0.0005005074335733273</v>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J115" t="n">
         <v>15.00956948650922</v>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>Enterobacter cloacae</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>Carbapenems</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D116" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E116" t="n">
-        <v>9</v>
-      </c>
-      <c r="F116" t="n">
-        <v>9</v>
-      </c>
-      <c r="G116" t="n">
-        <v>0.3186709066608939</v>
-      </c>
-      <c r="H116" t="n">
-        <v>0.3177832877260522</v>
-      </c>
-      <c r="I116" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J116" t="n">
-        <v>29.02802976333093</v>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
-        <is>
-          <t>Pseudomonas aeruginosa</t>
-        </is>
-      </c>
-      <c r="B117" t="inlineStr">
-        <is>
-          <t>Monobactams</t>
-        </is>
-      </c>
-      <c r="C117" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D117" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E117" t="n">
-        <v>9</v>
-      </c>
-      <c r="F117" t="n">
-        <v>9</v>
-      </c>
-      <c r="G117" t="n">
-        <v>0.09915702488602651</v>
-      </c>
-      <c r="H117" t="n">
-        <v>0.09855696370703471</v>
-      </c>
-      <c r="I117" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J117" t="n">
-        <v>34.01795504626856</v>
-      </c>
-    </row>
-    <row r="118">
-      <c r="A118" t="inlineStr">
-        <is>
-          <t>Enterococcus faecium</t>
-        </is>
-      </c>
-      <c r="B118" t="inlineStr">
-        <is>
-          <t>Penicillins</t>
-        </is>
-      </c>
-      <c r="C118" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D118" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E118" t="n">
-        <v>8</v>
-      </c>
-      <c r="F118" t="n">
-        <v>7</v>
-      </c>
-      <c r="G118" t="n">
-        <v>-0.08170085316266595</v>
-      </c>
-      <c r="H118" t="n">
-        <v>-0.1306111904464787</v>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J118" t="n">
-        <v>44.33250683049192</v>
-      </c>
-    </row>
-    <row r="119">
-      <c r="A119" t="inlineStr">
-        <is>
-          <t>Proteus mirabilis</t>
-        </is>
-      </c>
-      <c r="B119" t="inlineStr">
-        <is>
-          <t>Fluoroquinolones</t>
-        </is>
-      </c>
-      <c r="C119" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D119" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E119" t="n">
-        <v>8</v>
-      </c>
-      <c r="F119" t="n">
-        <v>9</v>
-      </c>
-      <c r="G119" t="n">
-        <v>0.2258148033630915</v>
-      </c>
-      <c r="H119" t="n">
-        <v>0.2571274692707208</v>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J119" t="n">
-        <v>29.09768211098879</v>
-      </c>
-    </row>
-    <row r="120">
-      <c r="A120" t="inlineStr">
-        <is>
-          <t>Acinetobacter baumannii</t>
-        </is>
-      </c>
-      <c r="B120" t="inlineStr">
-        <is>
-          <t>Penicillins</t>
-        </is>
-      </c>
-      <c r="C120" t="n">
-        <v>2024</v>
-      </c>
-      <c r="D120" t="n">
-        <v>2029</v>
-      </c>
-      <c r="E120" t="n">
-        <v>7</v>
-      </c>
-      <c r="F120" t="n">
-        <v>6</v>
-      </c>
-      <c r="G120" t="n">
-        <v>-0.246307983096238</v>
-      </c>
-      <c r="H120" t="n">
-        <v>-0.2784724403477783</v>
-      </c>
-      <c r="I120" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="J120" t="n">
-        <v>49.73997419211187</v>
       </c>
     </row>
   </sheetData>

--- a/archive/legacy_assets/predicted_SI.xlsx
+++ b/archive/legacy_assets/predicted_SI.xlsx
@@ -172,10 +172,10 @@
     <t>Oxazolidinones</t>
   </si>
   <si>
+    <t>yes</t>
+  </si>
+  <si>
     <t>no</t>
-  </si>
-  <si>
-    <t>yes</t>
   </si>
 </sst>
 </file>
@@ -626,7 +626,7 @@
         <v>1.183719002926647</v>
       </c>
       <c r="I3" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J3">
         <v>9.071585984706237</v>
@@ -658,7 +658,7 @@
         <v>1.002354953010338</v>
       </c>
       <c r="I4" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J4">
         <v>11.95780118076588</v>
@@ -690,7 +690,7 @@
         <v>1.101965783942812</v>
       </c>
       <c r="I5" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J5">
         <v>20.58756240828968</v>
@@ -754,7 +754,7 @@
         <v>0.9549592046414992</v>
       </c>
       <c r="I7" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J7">
         <v>17.37314067381907</v>
@@ -786,7 +786,7 @@
         <v>1.072414562207262</v>
       </c>
       <c r="I8" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J8">
         <v>20.50807269882524</v>
@@ -850,7 +850,7 @@
         <v>0.8313655914345222</v>
       </c>
       <c r="I10" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J10">
         <v>15.07591724190151</v>
@@ -882,7 +882,7 @@
         <v>1.004094691773939</v>
       </c>
       <c r="I11" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J11">
         <v>10.10437676892359</v>
@@ -914,7 +914,7 @@
         <v>0.9607544889622261</v>
       </c>
       <c r="I12" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J12">
         <v>8.091026715448415</v>
@@ -978,7 +978,7 @@
         <v>0.8074855164848718</v>
       </c>
       <c r="I14" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J14">
         <v>8.606093393731701</v>
@@ -1010,7 +1010,7 @@
         <v>0.8109736139487409</v>
       </c>
       <c r="I15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J15">
         <v>12.79660437093753</v>
@@ -1042,7 +1042,7 @@
         <v>0.725968350096911</v>
       </c>
       <c r="I16" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J16">
         <v>8.120475123713844</v>
@@ -1106,7 +1106,7 @@
         <v>0.6496044852505278</v>
       </c>
       <c r="I18" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J18">
         <v>12.74571639444505</v>
@@ -1170,7 +1170,7 @@
         <v>0.648211080546478</v>
       </c>
       <c r="I20" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J20">
         <v>10.02441052926776</v>
@@ -1202,7 +1202,7 @@
         <v>0.6670010548273044</v>
       </c>
       <c r="I21" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J21">
         <v>11.91071367370867</v>
@@ -1266,7 +1266,7 @@
         <v>0.6595287627412922</v>
       </c>
       <c r="I23" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J23">
         <v>24.87701442286552</v>
@@ -1298,7 +1298,7 @@
         <v>0.7818511801661132</v>
       </c>
       <c r="I24" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J24">
         <v>8.772103055789852</v>
@@ -1330,7 +1330,7 @@
         <v>0.778615562341779</v>
       </c>
       <c r="I25" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J25">
         <v>7.859441451082082</v>
@@ -1362,7 +1362,7 @@
         <v>0.7410264912224118</v>
       </c>
       <c r="I26" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J26">
         <v>4.382943702710341</v>
@@ -1426,7 +1426,7 @@
         <v>0.6466201601316135</v>
       </c>
       <c r="I28" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J28">
         <v>14.24201271075685</v>
@@ -1458,7 +1458,7 @@
         <v>0.7561400021450257</v>
       </c>
       <c r="I29" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J29">
         <v>14.51312263708803</v>
@@ -1490,7 +1490,7 @@
         <v>0.5657751756892995</v>
       </c>
       <c r="I30" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J30">
         <v>16.28469831565101</v>
@@ -1522,7 +1522,7 @@
         <v>0.4887199442023433</v>
       </c>
       <c r="I31" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J31">
         <v>23.95950368535706</v>
@@ -1554,7 +1554,7 @@
         <v>0.5389104496358017</v>
       </c>
       <c r="I32" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J32">
         <v>16.79577108345717</v>
@@ -1586,7 +1586,7 @@
         <v>0.7908885539092194</v>
       </c>
       <c r="I33" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J33">
         <v>5.915743582118907</v>
@@ -1618,7 +1618,7 @@
         <v>0.5052771290170388</v>
       </c>
       <c r="I34" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J34">
         <v>11.15986825894109</v>
@@ -1746,7 +1746,7 @@
         <v>0.5826070689387459</v>
       </c>
       <c r="I38" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J38">
         <v>13.92673290562042</v>
@@ -1778,7 +1778,7 @@
         <v>0.6142311679839063</v>
       </c>
       <c r="I39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="J39">
         <v>7.241672071835522</v>
@@ -1810,7 +1810,7 @@
         <v>0.3605213135780032</v>
       </c>
       <c r="I40" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J40">
         <v>9.405743123243324</v>
@@ -1874,7 +1874,7 @@
         <v>0.5060540892806709</v>
       </c>
       <c r="I42" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J42">
         <v>20.88899679499637</v>
@@ -1906,7 +1906,7 @@
         <v>0.3447164054891756</v>
       </c>
       <c r="I43" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J43">
         <v>19.30524576171661</v>
@@ -1970,7 +1970,7 @@
         <v>0.427074393790505</v>
       </c>
       <c r="I45" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J45">
         <v>13.19879367792396</v>
@@ -2002,7 +2002,7 @@
         <v>0.5214379594993712</v>
       </c>
       <c r="I46" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J46">
         <v>24.13876221942635</v>
@@ -2034,7 +2034,7 @@
         <v>0.5086773189739302</v>
       </c>
       <c r="I47" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J47">
         <v>16.93110445587214</v>
@@ -2066,7 +2066,7 @@
         <v>0.5134911045201391</v>
       </c>
       <c r="I48" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J48">
         <v>15.07270921511292</v>
@@ -2098,7 +2098,7 @@
         <v>0.341329375622631</v>
       </c>
       <c r="I49" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J49">
         <v>17.3435312125895</v>
@@ -2130,7 +2130,7 @@
         <v>0.292009319904533</v>
       </c>
       <c r="I50" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J50">
         <v>13.53437292203027</v>
@@ -2194,7 +2194,7 @@
         <v>0.3263571077129876</v>
       </c>
       <c r="I52" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J52">
         <v>9.43145036694629</v>
@@ -2226,7 +2226,7 @@
         <v>0.3897098508267349</v>
       </c>
       <c r="I53" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J53">
         <v>12.41451650350251</v>
@@ -2258,7 +2258,7 @@
         <v>0.5331781523858607</v>
       </c>
       <c r="I54" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J54">
         <v>15.90327209494377</v>
@@ -2290,7 +2290,7 @@
         <v>0.5088089694801923</v>
       </c>
       <c r="I55" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J55">
         <v>18.32872261437137</v>
@@ -2322,7 +2322,7 @@
         <v>0.5134988472317312</v>
       </c>
       <c r="I56" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J56">
         <v>11.83015226299159</v>
@@ -2354,7 +2354,7 @@
         <v>0.2727968421847911</v>
       </c>
       <c r="I57" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J57">
         <v>18.46621535578246</v>
@@ -2418,7 +2418,7 @@
         <v>0.5024493695731933</v>
       </c>
       <c r="I59" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J59">
         <v>14.10027015415705</v>
@@ -2450,7 +2450,7 @@
         <v>0.2032192238970947</v>
       </c>
       <c r="I60" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J60">
         <v>21.48445873543648</v>
@@ -2482,7 +2482,7 @@
         <v>0.4806698547503252</v>
       </c>
       <c r="I61" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J61">
         <v>22.02672963143239</v>
@@ -2514,7 +2514,7 @@
         <v>0.3105255081320208</v>
       </c>
       <c r="I62" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J62">
         <v>15.55108477810051</v>
@@ -2546,7 +2546,7 @@
         <v>0.5248496955731041</v>
       </c>
       <c r="I63" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J63">
         <v>21.64110764285963</v>
@@ -2610,7 +2610,7 @@
         <v>0.3892267651139838</v>
       </c>
       <c r="I65" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J65">
         <v>13.11248207792986</v>
@@ -2706,7 +2706,7 @@
         <v>0.2474241836001487</v>
       </c>
       <c r="I68" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J68">
         <v>11.56036807350337</v>
@@ -2770,7 +2770,7 @@
         <v>0.4332994565565464</v>
       </c>
       <c r="I70" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J70">
         <v>23.78244461515768</v>
@@ -2802,7 +2802,7 @@
         <v>0.4485706766248951</v>
       </c>
       <c r="I71" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J71">
         <v>14.91991941229707</v>
@@ -2834,7 +2834,7 @@
         <v>0.4771989178119607</v>
       </c>
       <c r="I72" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J72">
         <v>17.36455934537124</v>
@@ -2866,7 +2866,7 @@
         <v>0.2681090566240896</v>
       </c>
       <c r="I73" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J73">
         <v>20.31634113418007</v>
@@ -2898,7 +2898,7 @@
         <v>0.352298078666452</v>
       </c>
       <c r="I74" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J74">
         <v>15.93342650708624</v>
@@ -2962,7 +2962,7 @@
         <v>0.1592268907630912</v>
       </c>
       <c r="I76" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J76">
         <v>20.82430157481807</v>
@@ -3026,7 +3026,7 @@
         <v>0.124020270960528</v>
       </c>
       <c r="I78" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J78">
         <v>20.96651980317871</v>
@@ -3058,7 +3058,7 @@
         <v>0.2678481730624225</v>
       </c>
       <c r="I79" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J79">
         <v>24.49258294760917</v>
@@ -3090,7 +3090,7 @@
         <v>0.3132827272867045</v>
       </c>
       <c r="I80" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J80">
         <v>17.28943877287773</v>
@@ -3122,7 +3122,7 @@
         <v>0.3444331189228456</v>
       </c>
       <c r="I81" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J81">
         <v>20.46178265347313</v>
@@ -3154,7 +3154,7 @@
         <v>0.3071417659357354</v>
       </c>
       <c r="I82" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J82">
         <v>17.91631842151344</v>
@@ -3186,7 +3186,7 @@
         <v>-0.07191773300934057</v>
       </c>
       <c r="I83" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J83">
         <v>18.55981365758918</v>
@@ -3218,7 +3218,7 @@
         <v>0.0005005074335733273</v>
       </c>
       <c r="I84" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="J84">
         <v>15.00956948650922</v>
